--- a/data/processed/indicadores_ENV_SIEPAC.xlsx
+++ b/data/processed/indicadores_ENV_SIEPAC.xlsx
@@ -778,7 +778,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Emisiones en 10³ t; población en miles; PIB en USD constantes 2015; producción bruta en GWh. Fuente: ENVs.xlsx del equipo.</t>
+          <t>Emisiones en 10³ t; población en miles; PIB en USD constantes 2015; producción bruta en GWh. Fuente: matriz ENVs.xlsx.</t>
         </is>
       </c>
     </row>
